--- a/analysis/econometrics_outputs/contdid/Graficos/unemployment/contdid_rf_continuous.xlsx
+++ b/analysis/econometrics_outputs/contdid/Graficos/unemployment/contdid_rf_continuous.xlsx
@@ -407,7 +407,7 @@
     <col min="5" max="5" width="8.96125" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="7.7825" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="8.96125" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="7.7825" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="8.96125" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="12.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="5.425" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="3.71" hidden="0" customWidth="1"/>
@@ -515,13 +515,13 @@
         <v>0.0166</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.0158</v>
+        <v>0.0654</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>-0.1186</v>
+        <v>-0.1933</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.1518</v>
+        <v>0.2265</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -543,16 +543,16 @@
         <v>0.0862</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.002</v>
+        <v>0.0487</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.0689</v>
+        <v>-0.0701</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.1034</v>
+        <v>0.2424</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>11</v>
@@ -571,13 +571,13 @@
         <v>0.0829</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.0444</v>
+        <v>0.0531</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>-0.298</v>
+        <v>-0.0874</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.4638</v>
+        <v>0.2533</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>10</v>
@@ -599,13 +599,13 @@
         <v>-0.0756</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.0565</v>
+        <v>0.0525</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>-0.5602</v>
+        <v>-0.244</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.409</v>
+        <v>0.0928</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -627,13 +627,13 @@
         <v>0.3533</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.0881</v>
+        <v>0.115</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>-0.4022</v>
+        <v>-0.0155</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>1.1089</v>
+        <v>0.7221</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -655,13 +655,13 @@
         <v>0.2877</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.0891</v>
+        <v>0.1134</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>-0.4763</v>
+        <v>-0.0761</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>1.0516</v>
+        <v>0.6515</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>10</v>
@@ -683,13 +683,13 @@
         <v>0.2136</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.05</v>
+        <v>0.0833</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-0.2153</v>
+        <v>-0.0536</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.6425</v>
+        <v>0.4808</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -711,13 +711,13 @@
         <v>-0.2914</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.0906</v>
+        <v>0.1312</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>-1.0678</v>
+        <v>-0.7121</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.4851</v>
+        <v>0.1294</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>10</v>
@@ -739,16 +739,16 @@
         <v>-0.2674</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.1169</v>
+        <v>0.0784</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>-1.2693</v>
+        <v>-0.5188</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.7345</v>
+        <v>-0.016</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>11</v>
@@ -767,13 +767,13 @@
         <v>-0.1092</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.0808</v>
+        <v>0.0648</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>-0.802</v>
+        <v>-0.3171</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.5835</v>
+        <v>0.0986</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>10</v>
@@ -795,16 +795,16 @@
         <v>-0.3444</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.1122</v>
+        <v>0.1071</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>-1.3061</v>
+        <v>-0.688</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.6173</v>
+        <v>-0.0008</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>11</v>
@@ -823,13 +823,13 @@
         <v>0.1067</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.0893</v>
+        <v>0.0774</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>-0.6585</v>
+        <v>-0.1415</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.872</v>
+        <v>0.3549</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>10</v>
@@ -851,13 +851,13 @@
         <v>-0.0932</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.0585</v>
+        <v>0.0777</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>-0.5943</v>
+        <v>-0.3423</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>0.408</v>
+        <v>0.156</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>10</v>
@@ -879,13 +879,13 @@
         <v>-0.0851</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.0546</v>
+        <v>0.0526</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>-0.5528</v>
+        <v>-0.2538</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>0.3826</v>
+        <v>0.0836</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>10</v>
@@ -907,13 +907,13 @@
         <v>-0.0574</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.0531</v>
+        <v>0.072</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>-0.5126</v>
+        <v>-0.2885</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0.3979</v>
+        <v>0.1737</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>10</v>
@@ -935,13 +935,13 @@
         <v>0.0225</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.0778</v>
+        <v>0.0775</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>-0.6444</v>
+        <v>-0.2262</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.6893</v>
+        <v>0.2711</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>10</v>
@@ -963,16 +963,16 @@
         <v>0.3229</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.0604</v>
+        <v>0.0815</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>-0.1949</v>
+        <v>0.0616</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.8406</v>
+        <v>0.5841</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>11</v>
@@ -991,16 +991,16 @@
         <v>0.482</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.0861</v>
+        <v>0.083</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>-0.2559</v>
+        <v>0.2158</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>1.2198</v>
+        <v>0.7482</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>11</v>
@@ -1019,13 +1019,13 @@
         <v>0.2656</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.0506</v>
+        <v>0.0898</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>-0.1686</v>
+        <v>-0.0224</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.6997</v>
+        <v>0.5535</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>10</v>
@@ -1047,13 +1047,13 @@
         <v>-0.1162</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.0944</v>
+        <v>0.1087</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>-0.9253</v>
+        <v>-0.465</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>0.6928</v>
+        <v>0.2325</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>10</v>
@@ -1075,13 +1075,13 @@
         <v>-0.0632</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.2575</v>
+        <v>0.1492</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>-2.2701</v>
+        <v>-0.5419</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>2.1437</v>
+        <v>0.4155</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>10</v>
@@ -1103,13 +1103,13 @@
         <v>0.0262</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.0505</v>
+        <v>0.2036</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>-0.4071</v>
+        <v>-0.6268</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.4595</v>
+        <v>0.6791</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>10</v>
@@ -1131,13 +1131,13 @@
         <v>-0.0523</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>0.2375</v>
+        <v>0.1492</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>-2.0879</v>
+        <v>-0.531</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>1.9832</v>
+        <v>0.4263</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>10</v>
@@ -1159,13 +1159,13 @@
         <v>-0.0769</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>0.0676</v>
+        <v>0.174</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>-0.6567</v>
+        <v>-0.635</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>0.5029</v>
+        <v>0.4812</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>10</v>
@@ -1187,13 +1187,13 @@
         <v>-0.0469</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>0.1406</v>
+        <v>0.2195</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>-1.2519</v>
+        <v>-0.7511</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>1.1581</v>
+        <v>0.6573</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>10</v>
@@ -1215,13 +1215,13 @@
         <v>0.1254</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>0.0199</v>
+        <v>0.2398</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>-0.0455</v>
+        <v>-0.6437</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0.2963</v>
+        <v>0.8946</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>10</v>
@@ -1243,13 +1243,13 @@
         <v>0.1853</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>0.0916</v>
+        <v>0.218</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>-0.6001</v>
+        <v>-0.514</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>0.9706</v>
+        <v>0.8846</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>10</v>
@@ -1271,13 +1271,13 @@
         <v>0.157</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>0.1212</v>
+        <v>0.2175</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>-0.8822</v>
+        <v>-0.5407</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>1.1963</v>
+        <v>0.8548</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>10</v>
@@ -1299,13 +1299,13 @@
         <v>0.5353</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>0.2293</v>
+        <v>0.2304</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>-1.4305</v>
+        <v>-0.2037</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>2.5011</v>
+        <v>1.2743</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>10</v>
@@ -1327,13 +1327,13 @@
         <v>1.0312</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>0.0783</v>
+        <v>0.174</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>0.3597</v>
+        <v>0.4729</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>1.7026</v>
+        <v>1.5894</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>12</v>
@@ -1355,16 +1355,16 @@
         <v>1.2098</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>0.1518</v>
+        <v>0.1848</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>-0.0918</v>
+        <v>0.6169</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>2.5113</v>
+        <v>1.8026</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>13</v>
@@ -1383,16 +1383,16 @@
         <v>1.039</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0.1286</v>
+        <v>0.2084</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>-0.0634</v>
+        <v>0.3703</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>2.1413</v>
+        <v>1.7076</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>13</v>
@@ -1411,13 +1411,13 @@
         <v>0.8766</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.0563</v>
+        <v>0.208</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>0.3938</v>
+        <v>0.2094</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>1.3594</v>
+        <v>1.5438</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>12</v>
@@ -1439,13 +1439,13 @@
         <v>0.853</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0.0703</v>
+        <v>0.2521</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>0.2503</v>
+        <v>0.0442</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>1.4557</v>
+        <v>1.6618</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>12</v>
@@ -1467,13 +1467,13 @@
         <v>0.5918</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>0.1671</v>
+        <v>0.1882</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>-0.8401</v>
+        <v>-0.012</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>2.0237</v>
+        <v>1.1957</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>10</v>
@@ -1495,13 +1495,13 @@
         <v>0.6703</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0.1822</v>
+        <v>0.295</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>-0.8913</v>
+        <v>-0.2762</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>2.2318</v>
+        <v>1.6167</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>10</v>
@@ -1523,13 +1523,13 @@
         <v>0.6995</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>0.2767</v>
+        <v>0.2696</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>-1.6722</v>
+        <v>-0.1652</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>3.0713</v>
+        <v>1.5643</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>10</v>
@@ -1551,13 +1551,13 @@
         <v>0.7662</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>0.1004</v>
+        <v>0.2446</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>-0.0947</v>
+        <v>-0.0184</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>1.6271</v>
+        <v>1.5507</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>10</v>
@@ -1579,16 +1579,16 @@
         <v>0.8629</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0.3429</v>
+        <v>0.2678</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>-2.076</v>
+        <v>0.0037</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>3.8018</v>
+        <v>1.722</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J44" s="1" t="s">
         <v>13</v>
@@ -1607,13 +1607,13 @@
         <v>0.9208</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>0.1468</v>
+        <v>0.3333</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>-0.3372</v>
+        <v>-0.1484</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>2.1787</v>
+        <v>1.99</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>10</v>
@@ -1635,16 +1635,16 @@
         <v>1.2361</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.2915</v>
+        <v>0.3252</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>-1.2625</v>
+        <v>0.1931</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>3.7347</v>
+        <v>2.2792</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>13</v>
@@ -1663,16 +1663,16 @@
         <v>1.5324</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>0.2054</v>
+        <v>0.2414</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>-0.2283</v>
+        <v>0.7581</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>3.2932</v>
+        <v>2.3067</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J47" s="1" t="s">
         <v>13</v>
@@ -1691,13 +1691,13 @@
         <v>1.8452</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>0.1054</v>
+        <v>0.2311</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>0.9416</v>
+        <v>1.104</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>2.7489</v>
+        <v>2.5865</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>12</v>
@@ -1719,13 +1719,13 @@
         <v>1.7021</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>0.134</v>
+        <v>0.3197</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>0.5536</v>
+        <v>0.6765</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>2.8507</v>
+        <v>2.7278</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>12</v>
@@ -1747,13 +1747,13 @@
         <v>1.5887</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>0.1433</v>
+        <v>0.3438</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>0.3608</v>
+        <v>0.486</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>2.8166</v>
+        <v>2.6914</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>12</v>
@@ -1775,13 +1775,13 @@
         <v>1.579</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>0.0751</v>
+        <v>0.2826</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>0.9354</v>
+        <v>0.6723</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>2.2225</v>
+        <v>2.4856</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>12</v>
@@ -1803,13 +1803,13 @@
         <v>1.5973</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>0.1787</v>
+        <v>0.2728</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>0.0656</v>
+        <v>0.7222</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>3.129</v>
+        <v>2.4725</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>12</v>
@@ -1831,13 +1831,13 @@
         <v>1.7869</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>0.1551</v>
+        <v>0.3753</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>0.457</v>
+        <v>0.583</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>3.1167</v>
+        <v>2.9907</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>12</v>
@@ -1859,13 +1859,13 @@
         <v>1.8973</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>0.1543</v>
+        <v>0.3619</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>0.5746</v>
+        <v>0.7365</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>3.2201</v>
+        <v>3.0582</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>12</v>
@@ -1887,16 +1887,16 @@
         <v>1.811</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>0.4321</v>
+        <v>0.3639</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>-1.8931</v>
+        <v>0.6437</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>5.5151</v>
+        <v>2.9784</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J55" s="1" t="s">
         <v>13</v>
@@ -1915,13 +1915,13 @@
         <v>1.7928</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>0.03</v>
+        <v>0.2882</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>1.536</v>
+        <v>0.8685</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>2.0497</v>
+        <v>2.7172</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>12</v>
@@ -1943,13 +1943,13 @@
         <v>1.9801</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>0.0629</v>
+        <v>0.3984</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>1.4409</v>
+        <v>0.7021</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>2.5193</v>
+        <v>3.2581</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>12</v>
@@ -1971,13 +1971,13 @@
         <v>2.1385</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>0.1393</v>
+        <v>0.363</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>0.9442</v>
+        <v>0.974</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>3.3328</v>
+        <v>3.303</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>12</v>
@@ -1999,13 +1999,13 @@
         <v>2.7917</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>0.311</v>
+        <v>0.5402</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>0.126</v>
+        <v>1.0588</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>5.4574</v>
+        <v>4.5246</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>12</v>
@@ -2027,16 +2027,16 @@
         <v>3.0151</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>0.4223</v>
+        <v>0.3325</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>-0.6049</v>
+        <v>1.9484</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>6.6351</v>
+        <v>4.0818</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J60" s="1" t="s">
         <v>13</v>
@@ -2055,13 +2055,13 @@
         <v>2.6321</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>0.1584</v>
+        <v>0.4194</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>1.2746</v>
+        <v>1.2867</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>3.9897</v>
+        <v>3.9776</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>12</v>
@@ -2083,16 +2083,16 @@
         <v>2.5847</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>0.6439</v>
+        <v>0.4224</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>-2.9348</v>
+        <v>1.2298</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>8.1043</v>
+        <v>3.9397</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J62" s="1" t="s">
         <v>13</v>
@@ -2111,13 +2111,13 @@
         <v>2.6221</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>0.2846</v>
+        <v>0.4425</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>0.1824</v>
+        <v>1.2026</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>5.0618</v>
+        <v>4.0416</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>12</v>
@@ -2139,13 +2139,13 @@
         <v>2.6311</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>0.2862</v>
+        <v>0.4777</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>0.1781</v>
+        <v>1.0986</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>5.0842</v>
+        <v>4.1637</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>12</v>
@@ -2167,16 +2167,16 @@
         <v>2.6525</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>0.4282</v>
+        <v>0.3381</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>-1.018</v>
+        <v>1.5679</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>6.3229</v>
+        <v>3.737</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>13</v>
@@ -2195,16 +2195,16 @@
         <v>2.6463</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>0.3369</v>
+        <v>0.501</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>-0.2412</v>
+        <v>1.039</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>5.5338</v>
+        <v>4.2535</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J66" s="1" t="s">
         <v>13</v>
@@ -2223,13 +2223,13 @@
         <v>2.9081</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>0.3247</v>
+        <v>0.3836</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>0.125</v>
+        <v>1.6777</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>5.6912</v>
+        <v>4.1385</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>12</v>
